--- a/resources/MatriceDB.xlsx
+++ b/resources/MatriceDB.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AI Rediness-Maturity" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AI Readiness-Maturity" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
